--- a/research/traditional_assets/database/data/france/france_transportation_railroads.xlsx
+++ b/research/traditional_assets/database/data/france/france_transportation_railroads.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.456</v>
+        <v>-0.669</v>
       </c>
       <c r="E2">
-        <v>-0.172</v>
+        <v>-0.183</v>
       </c>
       <c r="G2">
-        <v>0.1149779735682819</v>
+        <v>7.081339712918661</v>
       </c>
       <c r="H2">
-        <v>0.1149779735682819</v>
+        <v>7.081339712918661</v>
       </c>
       <c r="I2">
-        <v>-0.006960352422907489</v>
+        <v>-4.502392344497608</v>
       </c>
       <c r="J2">
-        <v>-0.005832021787968924</v>
+        <v>-3.425733305596006</v>
       </c>
       <c r="K2">
-        <v>29.9</v>
+        <v>16.7</v>
       </c>
       <c r="L2">
-        <v>0.4390602055800294</v>
+        <v>79.90430622009569</v>
       </c>
       <c r="M2">
-        <v>119.5</v>
+        <v>105.4</v>
       </c>
       <c r="N2">
-        <v>0.02696421318651564</v>
+        <v>0.03055072463768116</v>
       </c>
       <c r="O2">
-        <v>3.996655518394649</v>
+        <v>6.311377245508982</v>
       </c>
       <c r="P2">
-        <v>119.5</v>
+        <v>105.4</v>
       </c>
       <c r="Q2">
-        <v>0.02696421318651564</v>
+        <v>0.03055072463768116</v>
       </c>
       <c r="R2">
-        <v>3.996655518394649</v>
+        <v>6.311377245508982</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,64 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1384</v>
+        <v>1069.6</v>
       </c>
       <c r="V2">
-        <v>0.3122884606706079</v>
+        <v>0.3100289855072463</v>
       </c>
       <c r="W2">
-        <v>0.009272467902995719</v>
+        <v>0.003561071306721255</v>
       </c>
       <c r="X2">
-        <v>0.04531448115852264</v>
+        <v>0.07535293367081805</v>
       </c>
       <c r="Y2">
-        <v>-0.03604201325552692</v>
+        <v>-0.07179186236409679</v>
       </c>
       <c r="Z2">
-        <v>0.03832948725164631</v>
+        <v>6.237502611394634e-05</v>
       </c>
       <c r="AA2">
-        <v>-0.0002235384047732784</v>
+        <v>-0.0002136802043959665</v>
       </c>
       <c r="AB2">
-        <v>0.04505490961596507</v>
+        <v>0.07533255628706795</v>
       </c>
       <c r="AC2">
-        <v>-0.04527844802073835</v>
+        <v>-0.07554623649146391</v>
       </c>
       <c r="AD2">
-        <v>46.4</v>
+        <v>1.99</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>46.4</v>
+        <v>1.99</v>
       </c>
       <c r="AG2">
-        <v>-1337.6</v>
+        <v>-1067.61</v>
       </c>
       <c r="AH2">
-        <v>0.01036130588182752</v>
+        <v>0.0005764790743889756</v>
       </c>
       <c r="AI2">
-        <v>0.009356159135361846</v>
+        <v>0.0005018168797076854</v>
       </c>
       <c r="AJ2">
-        <v>-0.4322926766207743</v>
+        <v>-0.4481256217495875</v>
       </c>
       <c r="AK2">
-        <v>-0.3741224512628311</v>
+        <v>-0.3686511348450789</v>
       </c>
       <c r="AL2">
-        <v>0.119</v>
+        <v>0</v>
       </c>
       <c r="AM2">
-        <v>-15.381</v>
-      </c>
-      <c r="AN2">
-        <v>5.149833518312986</v>
-      </c>
-      <c r="AO2">
-        <v>-3.983193277310924</v>
-      </c>
-      <c r="AP2">
-        <v>-148.4572697003329</v>
+        <v>-13.1</v>
       </c>
       <c r="AQ2">
-        <v>0.03081724205188219</v>
+        <v>0.07183206106870228</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +713,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.456</v>
+        <v>-0.669</v>
       </c>
       <c r="E3">
-        <v>-0.172</v>
+        <v>-0.183</v>
       </c>
       <c r="G3">
-        <v>0.1149779735682819</v>
+        <v>7.081339712918661</v>
       </c>
       <c r="H3">
-        <v>0.1149779735682819</v>
+        <v>7.081339712918661</v>
       </c>
       <c r="I3">
-        <v>-0.006960352422907489</v>
+        <v>-4.502392344497608</v>
       </c>
       <c r="J3">
-        <v>-0.005832021787968924</v>
+        <v>-3.425733305596006</v>
       </c>
       <c r="K3">
-        <v>29.9</v>
+        <v>16.7</v>
       </c>
       <c r="L3">
-        <v>0.4390602055800294</v>
+        <v>79.90430622009569</v>
       </c>
       <c r="M3">
-        <v>119.5</v>
+        <v>105.4</v>
       </c>
       <c r="N3">
-        <v>0.02696421318651564</v>
+        <v>0.03055072463768116</v>
       </c>
       <c r="O3">
-        <v>3.996655518394649</v>
+        <v>6.311377245508982</v>
       </c>
       <c r="P3">
-        <v>119.5</v>
+        <v>105.4</v>
       </c>
       <c r="Q3">
-        <v>0.02696421318651564</v>
+        <v>0.03055072463768116</v>
       </c>
       <c r="R3">
-        <v>3.996655518394649</v>
+        <v>6.311377245508982</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +761,64 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1384</v>
+        <v>1069.6</v>
       </c>
       <c r="V3">
-        <v>0.3122884606706079</v>
+        <v>0.3100289855072463</v>
       </c>
       <c r="W3">
-        <v>0.009272467902995719</v>
+        <v>0.003561071306721255</v>
       </c>
       <c r="X3">
-        <v>0.04531448115852264</v>
+        <v>0.07535293367081805</v>
       </c>
       <c r="Y3">
-        <v>-0.03604201325552692</v>
+        <v>-0.07179186236409679</v>
       </c>
       <c r="Z3">
-        <v>0.03832948725164631</v>
+        <v>6.237502611394634e-05</v>
       </c>
       <c r="AA3">
-        <v>-0.0002235384047732784</v>
+        <v>-0.0002136802043959665</v>
       </c>
       <c r="AB3">
-        <v>0.04505490961596507</v>
+        <v>0.07533255628706795</v>
       </c>
       <c r="AC3">
-        <v>-0.04527844802073835</v>
+        <v>-0.07554623649146391</v>
       </c>
       <c r="AD3">
-        <v>46.4</v>
+        <v>1.99</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>46.4</v>
+        <v>1.99</v>
       </c>
       <c r="AG3">
-        <v>-1337.6</v>
+        <v>-1067.61</v>
       </c>
       <c r="AH3">
-        <v>0.01036130588182752</v>
+        <v>0.0005764790743889756</v>
       </c>
       <c r="AI3">
-        <v>0.009356159135361846</v>
+        <v>0.0005018168797076854</v>
       </c>
       <c r="AJ3">
-        <v>-0.4322926766207743</v>
+        <v>-0.4481256217495875</v>
       </c>
       <c r="AK3">
-        <v>-0.3741224512628311</v>
+        <v>-0.3686511348450789</v>
       </c>
       <c r="AL3">
-        <v>0.119</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>-15.381</v>
-      </c>
-      <c r="AN3">
-        <v>5.149833518312986</v>
-      </c>
-      <c r="AO3">
-        <v>-3.983193277310924</v>
-      </c>
-      <c r="AP3">
-        <v>-148.4572697003329</v>
+        <v>-13.1</v>
       </c>
       <c r="AQ3">
-        <v>0.03081724205188219</v>
+        <v>0.07183206106870228</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/france/france_transportation_railroads.xlsx
+++ b/research/traditional_assets/database/data/france/france_transportation_railroads.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.669</v>
+        <v>-0.6779999999999999</v>
       </c>
       <c r="E2">
-        <v>-0.183</v>
+        <v>-0.49</v>
       </c>
       <c r="G2">
-        <v>7.081339712918661</v>
+        <v>-2.44954128440367</v>
       </c>
       <c r="H2">
-        <v>7.081339712918661</v>
+        <v>-2.44954128440367</v>
       </c>
       <c r="I2">
-        <v>-4.502392344497608</v>
+        <v>-4.004587155963303</v>
       </c>
       <c r="J2">
-        <v>-3.425733305596006</v>
+        <v>-3.208973813718938</v>
       </c>
       <c r="K2">
-        <v>16.7</v>
+        <v>22.3</v>
       </c>
       <c r="L2">
-        <v>79.90430622009569</v>
+        <v>102.2935779816514</v>
       </c>
       <c r="M2">
-        <v>105.4</v>
+        <v>110</v>
       </c>
       <c r="N2">
-        <v>0.03055072463768116</v>
+        <v>0.02735297774462265</v>
       </c>
       <c r="O2">
-        <v>6.311377245508982</v>
+        <v>4.932735426008969</v>
       </c>
       <c r="P2">
-        <v>105.4</v>
+        <v>110</v>
       </c>
       <c r="Q2">
-        <v>0.03055072463768116</v>
+        <v>0.02735297774462265</v>
       </c>
       <c r="R2">
-        <v>6.311377245508982</v>
+        <v>4.932735426008969</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,64 +636,64 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1069.6</v>
+        <v>969.9</v>
       </c>
       <c r="V2">
-        <v>0.3100289855072463</v>
+        <v>0.2411786646773592</v>
       </c>
       <c r="W2">
-        <v>0.003561071306721255</v>
+        <v>0.005826257348138472</v>
       </c>
       <c r="X2">
-        <v>0.07535293367081805</v>
+        <v>0.06506612505583974</v>
       </c>
       <c r="Y2">
-        <v>-0.07179186236409679</v>
+        <v>-0.05923986770770127</v>
       </c>
       <c r="Z2">
-        <v>6.237502611394634e-05</v>
+        <v>7.898865534495941e-05</v>
       </c>
       <c r="AA2">
-        <v>-0.0002136802043959665</v>
+        <v>-0.0002534725265828452</v>
       </c>
       <c r="AB2">
-        <v>0.07533255628706795</v>
+        <v>0.06506612505583974</v>
       </c>
       <c r="AC2">
-        <v>-0.07554623649146391</v>
+        <v>-0.06531959758242259</v>
       </c>
       <c r="AD2">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AG2">
-        <v>-1067.61</v>
+        <v>-969.9</v>
       </c>
       <c r="AH2">
-        <v>0.0005764790743889756</v>
+        <v>0</v>
       </c>
       <c r="AI2">
-        <v>0.0005018168797076854</v>
+        <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.4481256217495875</v>
+        <v>-0.3178332677939442</v>
       </c>
       <c r="AK2">
-        <v>-0.3686511348450789</v>
+        <v>-0.2282493587179065</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-13.1</v>
+        <v>-33.4</v>
       </c>
       <c r="AQ2">
-        <v>0.07183206106870228</v>
+        <v>0.0261377245508982</v>
       </c>
     </row>
     <row r="3">
@@ -713,46 +713,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.669</v>
+        <v>-0.6779999999999999</v>
       </c>
       <c r="E3">
-        <v>-0.183</v>
+        <v>-0.49</v>
       </c>
       <c r="G3">
-        <v>7.081339712918661</v>
+        <v>-2.44954128440367</v>
       </c>
       <c r="H3">
-        <v>7.081339712918661</v>
+        <v>-2.44954128440367</v>
       </c>
       <c r="I3">
-        <v>-4.502392344497608</v>
+        <v>-4.004587155963303</v>
       </c>
       <c r="J3">
-        <v>-3.425733305596006</v>
+        <v>-3.208973813718938</v>
       </c>
       <c r="K3">
-        <v>16.7</v>
+        <v>22.3</v>
       </c>
       <c r="L3">
-        <v>79.90430622009569</v>
+        <v>102.2935779816514</v>
       </c>
       <c r="M3">
-        <v>105.4</v>
+        <v>110</v>
       </c>
       <c r="N3">
-        <v>0.03055072463768116</v>
+        <v>0.02735297774462265</v>
       </c>
       <c r="O3">
-        <v>6.311377245508982</v>
+        <v>4.932735426008969</v>
       </c>
       <c r="P3">
-        <v>105.4</v>
+        <v>110</v>
       </c>
       <c r="Q3">
-        <v>0.03055072463768116</v>
+        <v>0.02735297774462265</v>
       </c>
       <c r="R3">
-        <v>6.311377245508982</v>
+        <v>4.932735426008969</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -761,64 +761,64 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1069.6</v>
+        <v>969.9</v>
       </c>
       <c r="V3">
-        <v>0.3100289855072463</v>
+        <v>0.2411786646773592</v>
       </c>
       <c r="W3">
-        <v>0.003561071306721255</v>
+        <v>0.005826257348138472</v>
       </c>
       <c r="X3">
-        <v>0.07535293367081805</v>
+        <v>0.06506612505583974</v>
       </c>
       <c r="Y3">
-        <v>-0.07179186236409679</v>
+        <v>-0.05923986770770127</v>
       </c>
       <c r="Z3">
-        <v>6.237502611394634e-05</v>
+        <v>7.898865534495941e-05</v>
       </c>
       <c r="AA3">
-        <v>-0.0002136802043959665</v>
+        <v>-0.0002534725265828452</v>
       </c>
       <c r="AB3">
-        <v>0.07533255628706795</v>
+        <v>0.06506612505583974</v>
       </c>
       <c r="AC3">
-        <v>-0.07554623649146391</v>
+        <v>-0.06531959758242259</v>
       </c>
       <c r="AD3">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>-1067.61</v>
+        <v>-969.9</v>
       </c>
       <c r="AH3">
-        <v>0.0005764790743889756</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>0.0005018168797076854</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.4481256217495875</v>
+        <v>-0.3178332677939442</v>
       </c>
       <c r="AK3">
-        <v>-0.3686511348450789</v>
+        <v>-0.2282493587179065</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-13.1</v>
+        <v>-33.4</v>
       </c>
       <c r="AQ3">
-        <v>0.07183206106870228</v>
+        <v>0.0261377245508982</v>
       </c>
     </row>
   </sheetData>
